--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,57 +811,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98706812</v>
+        <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100011</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Omkring Noppikoski, Dlr</t>
+          <t>Källmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493358</v>
+        <v>492868</v>
       </c>
       <c r="R3" t="n">
-        <v>6821465</v>
+        <v>6820649</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,27 +876,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>krets över toppen. FLD0008a (Calluna AB) örninventering</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,24 +906,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Frölinghaus</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98706812</t>
+          <t>https://artportalen.se/Sighting/137187907</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98706859</v>
+        <v>98706812</v>
       </c>
       <c r="B4" t="n">
         <v>57864</v>
@@ -981,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493316</v>
+        <v>493358</v>
       </c>
       <c r="R4" t="n">
-        <v>6821803</v>
+        <v>6821465</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,27 +997,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kort obs, tappas pga träd i förgrunden. FLD0008a (Calluna AB) örninventering</t>
+          <t>krets över toppen. FLD0008a (Calluna AB) örninventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,19 +1037,19 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Johan Frölinghaus</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98706859</t>
+          <t>https://artportalen.se/Sighting/98706812</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98706860</v>
+        <v>98706859</v>
       </c>
       <c r="B5" t="n">
         <v>57864</v>
@@ -1107,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493390</v>
+        <v>493316</v>
       </c>
       <c r="R5" t="n">
-        <v>6822071</v>
+        <v>6821803</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1142,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,12 +1138,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Förmodligen samma Råbergs-par som 14:25 FLD0008a (Calluna AB) örninventering</t>
+          <t>Kort obs, tappas pga träd i förgrunden. FLD0008a (Calluna AB) örninventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,39 +1163,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>John Kvarnbäck</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98706860</t>
+          <t>https://artportalen.se/Sighting/98706859</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98706885</v>
+        <v>98706860</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100067</v>
+        <v>100011</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1219,12 +1205,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1238,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493416</v>
+        <v>493390</v>
       </c>
       <c r="R6" t="n">
-        <v>6821403</v>
+        <v>6822071</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1268,27 +1249,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-02-28</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-02-28</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rörde sig ganska stationärt runt en uppstickande tall på Råberget FLD0008a (Calluna AB) örninventering</t>
+          <t>Förmodligen samma Råbergs-par som 14:25 FLD0008a (Calluna AB) örninventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1295,362 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/98706860</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98706885</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Omkring Noppikoski, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>493416</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6821403</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-02-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-02-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rörde sig ganska stationärt runt en uppstickande tall på Råberget FLD0008a (Calluna AB) örninventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>John Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/98706885</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137187824</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Källmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>492850</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6820602</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137187824</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137187940</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Källmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>492861</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6820661</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137187940</t>
         </is>
       </c>
     </row>
@@ -1325,6 +1661,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>137187824</v>
       </c>
       <c r="B8" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>137187940</v>
       </c>
       <c r="B9" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>137187824</v>
       </c>
       <c r="B8" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>137187940</v>
       </c>
       <c r="B9" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 533-2025 artfynd.xlsx
+++ b/artfynd/S 533-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>137187907</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
